--- a/languages/de/output/import/德语A1.xlsx
+++ b/languages/de/output/import/德语A1.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="词汇表" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="词汇表" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/languages/de/output/import/德语A1.xlsx
+++ b/languages/de/output/import/德语A1.xlsx
@@ -1075,7 +1075,7 @@
       </c>
       <c r="B21" s="1" t="inlineStr">
         <is>
-          <t>[das] （引导从句）〈konj.〉</t>
+          <t>[das] （引导从属从句）；即；表明〈konj.〉</t>
         </is>
       </c>
       <c r="C21" s="1" t="inlineStr">
@@ -1085,7 +1085,7 @@
       </c>
       <c r="D21" s="1" t="inlineStr">
         <is>
-          <t>（引导从句）</t>
+          <t>（引导从属从句）；即；表明</t>
         </is>
       </c>
       <c r="E21" s="1" t="inlineStr">
@@ -20883,7 +20883,7 @@
       </c>
       <c r="B640" s="1" t="inlineStr">
         <is>
-          <t>[oːʁanɡə] 橙子；橙色的〈n.f.〉</t>
+          <t>[oːʁanɡə] 橙子；柑橘〈n.f.〉</t>
         </is>
       </c>
       <c r="C640" s="1" t="inlineStr">
@@ -20893,7 +20893,7 @@
       </c>
       <c r="D640" s="1" t="inlineStr">
         <is>
-          <t>橙子；橙色的</t>
+          <t>橙子；柑橘</t>
         </is>
       </c>
       <c r="E640" s="1" t="inlineStr">

--- a/languages/de/output/import/德语A1.xlsx
+++ b/languages/de/output/import/德语A1.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="词汇表" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="词汇表" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -8435,12 +8435,12 @@
       </c>
       <c r="B251" s="1" t="inlineStr">
         <is>
-          <t>[ɛnt͡ʃʊldɪɡʊnk] 打扰一下；道歉〈n.f.〉</t>
+          <t>[ɛnt͡ʃʊldɪɡʊŋ] 打扰一下；道歉〈n.f.〉</t>
         </is>
       </c>
       <c r="C251" s="1" t="inlineStr">
         <is>
-          <t>ɛnt͡ʃʊldɪɡʊnk</t>
+          <t>ɛnt͡ʃʊldɪɡʊŋ</t>
         </is>
       </c>
       <c r="D251" s="1" t="inlineStr">
@@ -10419,12 +10419,12 @@
       </c>
       <c r="B313" s="1" t="inlineStr">
         <is>
-          <t>[voːnʊnk] 住房〈n.f.〉</t>
+          <t>[voːnʊŋ] 住房〈n.f.〉</t>
         </is>
       </c>
       <c r="C313" s="1" t="inlineStr">
         <is>
-          <t>voːnʊnk</t>
+          <t>voːnʊŋ</t>
         </is>
       </c>
       <c r="D313" s="1" t="inlineStr">
@@ -13811,12 +13811,12 @@
       </c>
       <c r="B419" s="1" t="inlineStr">
         <is>
-          <t>[t͡saɪtʊnk] 报纸〈n.f.〉</t>
+          <t>[t͡saɪtʊŋ] 报纸〈n.f.〉</t>
         </is>
       </c>
       <c r="C419" s="1" t="inlineStr">
         <is>
-          <t>t͡saɪtʊnk</t>
+          <t>t͡saɪtʊŋ</t>
         </is>
       </c>
       <c r="D419" s="1" t="inlineStr">
@@ -15347,12 +15347,12 @@
       </c>
       <c r="B467" s="1" t="inlineStr">
         <is>
-          <t>[fiːdɛɔ] 视频〈n.〉</t>
+          <t>[viːdeo] 视频〈n.〉</t>
         </is>
       </c>
       <c r="C467" s="1" t="inlineStr">
         <is>
-          <t>fiːdɛɔ</t>
+          <t>viːdeo</t>
         </is>
       </c>
       <c r="D467" s="1" t="inlineStr">
@@ -16723,12 +16723,12 @@
       </c>
       <c r="B510" s="1" t="inlineStr">
         <is>
-          <t>[klaɪdʊnk] 衣服〈n.f.〉</t>
+          <t>[klaɪdʊŋ] 衣服〈n.f.〉</t>
         </is>
       </c>
       <c r="C510" s="1" t="inlineStr">
         <is>
-          <t>klaɪdʊnk</t>
+          <t>klaɪdʊŋ</t>
         </is>
       </c>
       <c r="D510" s="1" t="inlineStr">
